--- a/artfynd/A 35744-2022 artfynd.xlsx
+++ b/artfynd/A 35744-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35744-2022 artfynd.xlsx
+++ b/artfynd/A 35744-2022 artfynd.xlsx
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117563019</v>
+        <v>117562993</v>
       </c>
       <c r="B12" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
         <v>501898</v>
       </c>
       <c r="R12" t="n">
-        <v>6923623</v>
+        <v>6923624</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117563018</v>
+        <v>117563002</v>
       </c>
       <c r="B13" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501990</v>
+        <v>501974</v>
       </c>
       <c r="R13" t="n">
-        <v>6923578</v>
+        <v>6923604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117562979</v>
+        <v>117563018</v>
       </c>
       <c r="B14" t="n">
-        <v>79562</v>
+        <v>78216</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,21 +2034,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501975</v>
+        <v>501990</v>
       </c>
       <c r="R14" t="n">
-        <v>6923603</v>
+        <v>6923578</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117563002</v>
+        <v>117563019</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501974</v>
+        <v>501898</v>
       </c>
       <c r="R15" t="n">
-        <v>6923604</v>
+        <v>6923623</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117562993</v>
+        <v>117562979</v>
       </c>
       <c r="B16" t="n">
-        <v>78217</v>
+        <v>79562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501898</v>
+        <v>501975</v>
       </c>
       <c r="R16" t="n">
-        <v>6923624</v>
+        <v>6923603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117859637</v>
+        <v>117859964</v>
       </c>
       <c r="B17" t="n">
         <v>97836</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501928</v>
+        <v>501869</v>
       </c>
       <c r="R17" t="n">
-        <v>6923624</v>
+        <v>6923619</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117863146</v>
+        <v>117859727</v>
       </c>
       <c r="B18" t="n">
         <v>97836</v>
@@ -2478,20 +2478,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502005</v>
+        <v>501907</v>
       </c>
       <c r="R18" t="n">
-        <v>6923581</v>
+        <v>6923667</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2518,14 +2527,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2540,22 +2554,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117863128</v>
+        <v>117863126</v>
       </c>
       <c r="B19" t="n">
-        <v>79069</v>
+        <v>79098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501974</v>
+        <v>502006</v>
       </c>
       <c r="R19" t="n">
-        <v>6923597</v>
+        <v>6923603</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2770,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117859964</v>
+        <v>117863147</v>
       </c>
       <c r="B21" t="n">
         <v>97836</v>
@@ -2789,29 +2803,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501869</v>
+        <v>501899</v>
       </c>
       <c r="R21" t="n">
-        <v>6923619</v>
+        <v>6923611</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2838,19 +2843,14 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:34</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,19 +2865,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117859727</v>
+        <v>117859637</v>
       </c>
       <c r="B22" t="n">
         <v>97836</v>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501907</v>
+        <v>501928</v>
       </c>
       <c r="R22" t="n">
-        <v>6923667</v>
+        <v>6923624</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117863136</v>
+        <v>117863128</v>
       </c>
       <c r="B25" t="n">
-        <v>78217</v>
+        <v>79069</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502006</v>
+        <v>501974</v>
       </c>
       <c r="R25" t="n">
-        <v>6923603</v>
+        <v>6923597</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3297,17 +3297,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117863150</v>
+        <v>117863146</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,25 +3316,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501976</v>
+        <v>502005</v>
       </c>
       <c r="R26" t="n">
-        <v>6923580</v>
+        <v>6923581</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,6 +3380,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3406,10 +3411,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117863147</v>
+        <v>117863150</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3418,25 +3423,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3451,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501899</v>
+        <v>501976</v>
       </c>
       <c r="R27" t="n">
-        <v>6923611</v>
+        <v>6923580</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,11 +3487,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3513,10 +3513,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117863126</v>
+        <v>117863136</v>
       </c>
       <c r="B28" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117883968</v>
+        <v>117883974</v>
       </c>
       <c r="B30" t="n">
-        <v>79561</v>
+        <v>91772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,25 +3729,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>501978</v>
+        <v>501974</v>
       </c>
       <c r="R30" t="n">
-        <v>6923605</v>
+        <v>6923604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117883974</v>
+        <v>117883968</v>
       </c>
       <c r="B31" t="n">
-        <v>91772</v>
+        <v>79561</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501974</v>
+        <v>501978</v>
       </c>
       <c r="R31" t="n">
-        <v>6923604</v>
+        <v>6923605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117883975</v>
+        <v>117883972</v>
       </c>
       <c r="B32" t="n">
-        <v>91772</v>
+        <v>97836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3933,38 +3933,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501997</v>
+        <v>501932</v>
       </c>
       <c r="R32" t="n">
-        <v>6923620</v>
+        <v>6923641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,6 +4013,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4016,17 +4025,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117883972</v>
+        <v>117883975</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>91772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4035,46 +4044,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501932</v>
+        <v>501997</v>
       </c>
       <c r="R33" t="n">
-        <v>6923641</v>
+        <v>6923620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4115,7 +4116,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 35744-2022 artfynd.xlsx
+++ b/artfynd/A 35744-2022 artfynd.xlsx
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117562993</v>
+        <v>117562979</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>79564</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501898</v>
+        <v>501975</v>
       </c>
       <c r="R12" t="n">
-        <v>6923624</v>
+        <v>6923603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117563002</v>
+        <v>117563018</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>78218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501974</v>
+        <v>501990</v>
       </c>
       <c r="R13" t="n">
-        <v>6923604</v>
+        <v>6923578</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117563018</v>
+        <v>117563019</v>
       </c>
       <c r="B14" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501990</v>
+        <v>501898</v>
       </c>
       <c r="R14" t="n">
-        <v>6923578</v>
+        <v>6923623</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117563019</v>
+        <v>117563002</v>
       </c>
       <c r="B15" t="n">
-        <v>78216</v>
+        <v>79563</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501898</v>
+        <v>501974</v>
       </c>
       <c r="R15" t="n">
-        <v>6923623</v>
+        <v>6923604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117562979</v>
+        <v>117562993</v>
       </c>
       <c r="B16" t="n">
-        <v>79562</v>
+        <v>78219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501975</v>
+        <v>501898</v>
       </c>
       <c r="R16" t="n">
-        <v>6923603</v>
+        <v>6923624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117859964</v>
+        <v>117863152</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,50 +2336,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501869</v>
+        <v>501939</v>
       </c>
       <c r="R17" t="n">
-        <v>6923619</v>
+        <v>6923629</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2406,19 +2397,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,22 +2414,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117859727</v>
+        <v>117863132</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>96793</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,50 +2438,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501907</v>
+        <v>501917</v>
       </c>
       <c r="R18" t="n">
-        <v>6923667</v>
+        <v>6923595</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2527,19 +2499,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,22 +2516,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117863126</v>
+        <v>117863135</v>
       </c>
       <c r="B19" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,21 +2544,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502006</v>
+        <v>501875</v>
       </c>
       <c r="R19" t="n">
-        <v>6923603</v>
+        <v>6923629</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,17 +2623,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117863135</v>
+        <v>117863147</v>
       </c>
       <c r="B20" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,25 +2642,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2708,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501875</v>
+        <v>501899</v>
       </c>
       <c r="R20" t="n">
-        <v>6923629</v>
+        <v>6923611</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,6 +2706,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117863147</v>
+        <v>117863136</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>78219</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2782,25 +2749,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2810,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501899</v>
+        <v>502006</v>
       </c>
       <c r="R21" t="n">
-        <v>6923611</v>
+        <v>6923603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,11 +2813,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,7 +2842,7 @@
         <v>117859637</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117863152</v>
+        <v>117859964</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3010,41 +2972,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501939</v>
+        <v>501869</v>
       </c>
       <c r="R23" t="n">
-        <v>6923629</v>
+        <v>6923619</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,9 +3042,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,22 +3069,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117863132</v>
+        <v>117863126</v>
       </c>
       <c r="B24" t="n">
-        <v>96791</v>
+        <v>79100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3112,25 +3093,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3121,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501917</v>
+        <v>502006</v>
       </c>
       <c r="R24" t="n">
-        <v>6923595</v>
+        <v>6923603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3195,17 +3176,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117863128</v>
+        <v>117863150</v>
       </c>
       <c r="B25" t="n">
-        <v>79069</v>
+        <v>78482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3218,21 +3199,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501974</v>
+        <v>501976</v>
       </c>
       <c r="R25" t="n">
-        <v>6923597</v>
+        <v>6923580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3297,17 +3278,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117863146</v>
+        <v>117863128</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>79071</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,25 +3297,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3344,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502005</v>
+        <v>501974</v>
       </c>
       <c r="R26" t="n">
-        <v>6923581</v>
+        <v>6923597</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3382,11 +3363,6 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>25 ex</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3404,17 +3380,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117863150</v>
+        <v>117863146</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3423,25 +3399,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3451,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501976</v>
+        <v>502005</v>
       </c>
       <c r="R27" t="n">
-        <v>6923580</v>
+        <v>6923581</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,6 +3463,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3513,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117863136</v>
+        <v>117859727</v>
       </c>
       <c r="B28" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3525,41 +3506,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502006</v>
+        <v>501907</v>
       </c>
       <c r="R28" t="n">
-        <v>6923603</v>
+        <v>6923667</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3586,9 +3576,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,22 +3603,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117883763</v>
+        <v>117883968</v>
       </c>
       <c r="B29" t="n">
-        <v>79562</v>
+        <v>79563</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3631,21 +3631,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3710,17 +3710,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117883974</v>
+        <v>117883972</v>
       </c>
       <c r="B30" t="n">
-        <v>91772</v>
+        <v>97838</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,38 +3729,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>501974</v>
+        <v>501932</v>
       </c>
       <c r="R30" t="n">
-        <v>6923604</v>
+        <v>6923641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3801,6 +3809,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3819,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117883968</v>
+        <v>117883763</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3835,21 +3844,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3914,17 +3923,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117883972</v>
+        <v>117883975</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
+        <v>91774</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3933,46 +3942,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501932</v>
+        <v>501997</v>
       </c>
       <c r="R32" t="n">
-        <v>6923641</v>
+        <v>6923620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,7 +4014,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117883975</v>
+        <v>117883974</v>
       </c>
       <c r="B33" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501997</v>
+        <v>501974</v>
       </c>
       <c r="R33" t="n">
-        <v>6923620</v>
+        <v>6923604</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
